--- a/artfynd/A 44869-2022 artfynd.xlsx
+++ b/artfynd/A 44869-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44869-2022 artfynd.xlsx
+++ b/artfynd/A 44869-2022 artfynd.xlsx
@@ -675,51 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104471534</v>
+        <v>104616719</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92281</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2062</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Patronbodarna Ö , Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477674.6942412693</v>
+        <v>477778</v>
       </c>
       <c r="R2" t="n">
-        <v>7019362.627564264</v>
+        <v>7019525</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +746,9 @@
           <t>2022-11-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-11-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,9 +757,39 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Äldre granskog, ganska städad men mindre partier med större inslag av död ved.</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Svamp, fruktkropp mm</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Fungi, fruit bodies, etc. # Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -781,60 +798,56 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Råghall, Benny Öwre, Kristofer Holmsten</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104478312</v>
+        <v>104471534</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Patronbodarna, Jmt</t>
+          <t>Patronbodarna Ö , Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477654.183709215</v>
+        <v>477674</v>
       </c>
       <c r="R3" t="n">
-        <v>7019392.000953268</v>
+        <v>7019363</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,19 +874,9 @@
           <t>2022-11-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-11-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,12 +891,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Kristofer Holmsten</t>
+          <t>Johan Råghall, Benny Öwre, Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -903,12 +906,7 @@
         <v>104471741</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477667.9049499093</v>
+        <v>477668</v>
       </c>
       <c r="R4" t="n">
-        <v>7019422.485323902</v>
+        <v>7019422</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,19 +972,9 @@
           <t>2022-11-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-11-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,15 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104616719</v>
+        <v>104478312</v>
       </c>
       <c r="B5" t="n">
-        <v>89732</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1029,40 +1012,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Patronbodarna Ö , Jmt</t>
+          <t>Patronbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477777.5869151625</v>
+        <v>477654</v>
       </c>
       <c r="R5" t="n">
-        <v>7019524.704782582</v>
+        <v>7019392</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,19 +1069,9 @@
           <t>2022-11-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-11-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,48 +1080,18 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Äldre granskog, ganska städad men mindre partier med större inslag av död ved.</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Svamp, fruktkropp mm</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Fungi, fruit bodies, etc. # Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre, Johan Råghall, Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 44869-2022 artfynd.xlsx
+++ b/artfynd/A 44869-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -802,6 +807,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104616719</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104471534</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104471741</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,8 +1115,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104478312</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>